--- a/src/Verify.OpenXml.Tests/ExcelProtectionTests.Protection.verified.xlsx
+++ b/src/Verify.OpenXml.Tests/ExcelProtectionTests.Protection.verified.xlsx
@@ -20,5 +20,6 @@
     </row>
   </sheetData>
   <sheetProtection password="DAA7" sheet="1" objects="1" scenarios="1" formatCells="1" formatColumns="1" formatRows="1" insertColumns="1" insertRows="1" insertHyperlinks="1" deleteColumns="1" deleteRows="1" selectLockedCells="0" sort="0" autoFilter="0" pivotTables="1" selectUnlockedCells="0"/>
+  <pageSetup paperSize="9"/>
 </worksheet>
 </file>
--- a/src/Verify.OpenXml.Tests/ExcelProtectionTests.Protection.verified.xlsx
+++ b/src/Verify.OpenXml.Tests/ExcelProtectionTests.Protection.verified.xlsx
@@ -20,6 +20,5 @@
     </row>
   </sheetData>
   <sheetProtection password="DAA7" sheet="1" objects="1" scenarios="1" formatCells="1" formatColumns="1" formatRows="1" insertColumns="1" insertRows="1" insertHyperlinks="1" deleteColumns="1" deleteRows="1" selectLockedCells="0" sort="0" autoFilter="0" pivotTables="1" selectUnlockedCells="0"/>
-  <pageSetup paperSize="9"/>
 </worksheet>
 </file>